--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122605578</v>
+        <v>122607745</v>
       </c>
       <c r="B2" t="n">
         <v>94727</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599123</v>
+        <v>599042</v>
       </c>
       <c r="R2" t="n">
-        <v>6371303</v>
+        <v>6371309</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611560</v>
+        <v>122607634</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>57402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,48 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599157</v>
+        <v>599119</v>
       </c>
       <c r="R3" t="n">
-        <v>6371219</v>
+        <v>6371267</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,28 +850,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607634</v>
+        <v>122607678</v>
       </c>
       <c r="B4" t="n">
-        <v>57402</v>
+        <v>94727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599119</v>
+        <v>599125</v>
       </c>
       <c r="R4" t="n">
-        <v>6371267</v>
+        <v>6371302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607745</v>
+        <v>122605621</v>
       </c>
       <c r="B5" t="n">
         <v>94727</v>
@@ -1039,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599042</v>
+        <v>599116</v>
       </c>
       <c r="R5" t="n">
-        <v>6371309</v>
+        <v>6371319</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607678</v>
+        <v>122605578</v>
       </c>
       <c r="B6" t="n">
         <v>94727</v>
@@ -1141,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599125</v>
+        <v>599123</v>
       </c>
       <c r="R6" t="n">
-        <v>6371302</v>
+        <v>6371303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122605621</v>
+        <v>122611560</v>
       </c>
       <c r="B7" t="n">
-        <v>94727</v>
+        <v>90859</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,41 +1197,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599116</v>
+        <v>599157</v>
       </c>
       <c r="R7" t="n">
-        <v>6371319</v>
+        <v>6371219</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,17 +1265,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607745</v>
+        <v>122611560</v>
       </c>
       <c r="B2" t="n">
-        <v>94727</v>
+        <v>90853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599042</v>
+        <v>599157</v>
       </c>
       <c r="R2" t="n">
-        <v>6371309</v>
+        <v>6371219</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,17 +755,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607634</v>
+        <v>122607745</v>
       </c>
       <c r="B3" t="n">
-        <v>57402</v>
+        <v>94729</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599119</v>
+        <v>599042</v>
       </c>
       <c r="R3" t="n">
-        <v>6371267</v>
+        <v>6371309</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607678</v>
+        <v>122607634</v>
       </c>
       <c r="B4" t="n">
-        <v>94727</v>
+        <v>57402</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599125</v>
+        <v>599119</v>
       </c>
       <c r="R4" t="n">
-        <v>6371302</v>
+        <v>6371267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +1002,7 @@
         <v>122605621</v>
       </c>
       <c r="B5" t="n">
-        <v>94727</v>
+        <v>94729</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,7 +1104,7 @@
         <v>122605578</v>
       </c>
       <c r="B6" t="n">
-        <v>94727</v>
+        <v>94729</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122611560</v>
+        <v>122607678</v>
       </c>
       <c r="B7" t="n">
-        <v>90859</v>
+        <v>94729</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,48 +1215,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599157</v>
+        <v>599125</v>
       </c>
       <c r="R7" t="n">
-        <v>6371219</v>
+        <v>6371302</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1265,28 +1276,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611560</v>
+        <v>122607745</v>
       </c>
       <c r="B2" t="n">
-        <v>90853</v>
+        <v>94729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599157</v>
+        <v>599042</v>
       </c>
       <c r="R2" t="n">
-        <v>6371219</v>
+        <v>6371309</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,28 +748,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607745</v>
+        <v>122605621</v>
       </c>
       <c r="B3" t="n">
         <v>94729</v>
@@ -835,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599042</v>
+        <v>599116</v>
       </c>
       <c r="R3" t="n">
-        <v>6371309</v>
+        <v>6371319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607634</v>
+        <v>122607678</v>
       </c>
       <c r="B4" t="n">
-        <v>57402</v>
+        <v>94729</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599119</v>
+        <v>599125</v>
       </c>
       <c r="R4" t="n">
-        <v>6371267</v>
+        <v>6371302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122605621</v>
+        <v>122605578</v>
       </c>
       <c r="B5" t="n">
         <v>94729</v>
@@ -1039,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599116</v>
+        <v>599123</v>
       </c>
       <c r="R5" t="n">
-        <v>6371319</v>
+        <v>6371303</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122605578</v>
+        <v>122607634</v>
       </c>
       <c r="B6" t="n">
-        <v>94729</v>
+        <v>57402</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599123</v>
+        <v>599119</v>
       </c>
       <c r="R6" t="n">
-        <v>6371303</v>
+        <v>6371267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607678</v>
+        <v>122611560</v>
       </c>
       <c r="B7" t="n">
-        <v>94729</v>
+        <v>90853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,41 +1197,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599125</v>
+        <v>599157</v>
       </c>
       <c r="R7" t="n">
-        <v>6371302</v>
+        <v>6371219</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,17 +1265,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607745</v>
+        <v>122611560</v>
       </c>
       <c r="B2" t="n">
-        <v>94729</v>
+        <v>90854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599042</v>
+        <v>599157</v>
       </c>
       <c r="R2" t="n">
-        <v>6371309</v>
+        <v>6371219</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,17 +755,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122605621</v>
+        <v>122607634</v>
       </c>
       <c r="B3" t="n">
-        <v>94729</v>
+        <v>57403</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599116</v>
+        <v>599119</v>
       </c>
       <c r="R3" t="n">
-        <v>6371319</v>
+        <v>6371267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +900,7 @@
         <v>122607678</v>
       </c>
       <c r="B4" t="n">
-        <v>94729</v>
+        <v>94730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122605578</v>
+        <v>122607745</v>
       </c>
       <c r="B5" t="n">
-        <v>94729</v>
+        <v>94730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599123</v>
+        <v>599042</v>
       </c>
       <c r="R5" t="n">
-        <v>6371303</v>
+        <v>6371309</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607634</v>
+        <v>122605621</v>
       </c>
       <c r="B6" t="n">
-        <v>57402</v>
+        <v>94730</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599119</v>
+        <v>599116</v>
       </c>
       <c r="R6" t="n">
-        <v>6371267</v>
+        <v>6371319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122611560</v>
+        <v>122605578</v>
       </c>
       <c r="B7" t="n">
-        <v>90853</v>
+        <v>94730</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,48 +1215,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599157</v>
+        <v>599123</v>
       </c>
       <c r="R7" t="n">
-        <v>6371219</v>
+        <v>6371303</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1265,28 +1276,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122783407</v>
+        <v>122784093</v>
       </c>
       <c r="B8" t="n">
-        <v>90960</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,37 +1321,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598958</v>
+        <v>598954</v>
       </c>
       <c r="R8" t="n">
-        <v>6371064</v>
+        <v>6371068</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122785481</v>
+        <v>122782695</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>90904</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,42 +1427,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598943</v>
+        <v>599109</v>
       </c>
       <c r="R9" t="n">
-        <v>6371087</v>
+        <v>6371243</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122784093</v>
+        <v>122785740</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>94844</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,45 +1525,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598954</v>
+        <v>599069</v>
       </c>
       <c r="R10" t="n">
-        <v>6371068</v>
+        <v>6371302</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122782695</v>
+        <v>122782823</v>
       </c>
       <c r="B11" t="n">
-        <v>90900</v>
+        <v>94844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,25 +1627,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599109</v>
+        <v>599138</v>
       </c>
       <c r="R11" t="n">
-        <v>6371243</v>
+        <v>6371196</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1722,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122782823</v>
+        <v>122785481</v>
       </c>
       <c r="B12" t="n">
-        <v>94836</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,41 +1729,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599138</v>
+        <v>598943</v>
       </c>
       <c r="R12" t="n">
-        <v>6371196</v>
+        <v>6371087</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122785740</v>
+        <v>122783407</v>
       </c>
       <c r="B13" t="n">
-        <v>94836</v>
+        <v>90964</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,25 +1836,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599069</v>
+        <v>598958</v>
       </c>
       <c r="R13" t="n">
-        <v>6371302</v>
+        <v>6371064</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122605621</v>
+        <v>122611560</v>
       </c>
       <c r="B2" t="n">
-        <v>94836</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599116</v>
+        <v>599157</v>
       </c>
       <c r="R2" t="n">
-        <v>6371319</v>
+        <v>6371219</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,17 +755,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -882,7 +900,7 @@
         <v>122607745</v>
       </c>
       <c r="B4" t="n">
-        <v>94836</v>
+        <v>94844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,7 +1002,7 @@
         <v>122605578</v>
       </c>
       <c r="B5" t="n">
-        <v>94836</v>
+        <v>94844</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611560</v>
+        <v>122605621</v>
       </c>
       <c r="B6" t="n">
-        <v>90960</v>
+        <v>94844</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,48 +1113,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599157</v>
+        <v>599116</v>
       </c>
       <c r="R6" t="n">
-        <v>6371219</v>
+        <v>6371319</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,28 +1174,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>122607678</v>
       </c>
       <c r="B7" t="n">
-        <v>94836</v>
+        <v>94844</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611560</v>
+        <v>122605621</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>94844</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599157</v>
+        <v>599116</v>
       </c>
       <c r="R2" t="n">
-        <v>6371219</v>
+        <v>6371319</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,28 +748,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607634</v>
+        <v>122607745</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>94844</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599119</v>
+        <v>599042</v>
       </c>
       <c r="R3" t="n">
-        <v>6371267</v>
+        <v>6371309</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607745</v>
+        <v>122607678</v>
       </c>
       <c r="B4" t="n">
         <v>94844</v>
@@ -937,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599042</v>
+        <v>599125</v>
       </c>
       <c r="R4" t="n">
-        <v>6371309</v>
+        <v>6371302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122605578</v>
+        <v>122607634</v>
       </c>
       <c r="B5" t="n">
-        <v>94844</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599123</v>
+        <v>599119</v>
       </c>
       <c r="R5" t="n">
-        <v>6371303</v>
+        <v>6371267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122605621</v>
+        <v>122605578</v>
       </c>
       <c r="B6" t="n">
         <v>94844</v>
@@ -1141,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599116</v>
+        <v>599123</v>
       </c>
       <c r="R6" t="n">
-        <v>6371319</v>
+        <v>6371303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607678</v>
+        <v>122611560</v>
       </c>
       <c r="B7" t="n">
-        <v>94844</v>
+        <v>90964</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,41 +1197,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599125</v>
+        <v>599157</v>
       </c>
       <c r="R7" t="n">
-        <v>6371302</v>
+        <v>6371219</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,17 +1265,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122784093</v>
+        <v>122783407</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,41 +1321,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598954</v>
+        <v>598958</v>
       </c>
       <c r="R8" t="n">
-        <v>6371068</v>
+        <v>6371064</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1717,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122785481</v>
+        <v>122784093</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1733,27 +1729,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1762,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598943</v>
+        <v>598954</v>
       </c>
       <c r="R12" t="n">
-        <v>6371087</v>
+        <v>6371068</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1824,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122783407</v>
+        <v>122785481</v>
       </c>
       <c r="B13" t="n">
-        <v>90964</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1840,37 +1835,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598958</v>
+        <v>598943</v>
       </c>
       <c r="R13" t="n">
-        <v>6371064</v>
+        <v>6371087</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122605621</v>
+        <v>122607745</v>
       </c>
       <c r="B2" t="n">
-        <v>94844</v>
+        <v>94846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599116</v>
+        <v>599042</v>
       </c>
       <c r="R2" t="n">
-        <v>6371319</v>
+        <v>6371309</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607745</v>
+        <v>122605578</v>
       </c>
       <c r="B3" t="n">
-        <v>94844</v>
+        <v>94846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599042</v>
+        <v>599123</v>
       </c>
       <c r="R3" t="n">
-        <v>6371309</v>
+        <v>6371303</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607678</v>
+        <v>122607634</v>
       </c>
       <c r="B4" t="n">
-        <v>94844</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599125</v>
+        <v>599119</v>
       </c>
       <c r="R4" t="n">
-        <v>6371302</v>
+        <v>6371267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607634</v>
+        <v>122607678</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>94846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599119</v>
+        <v>599125</v>
       </c>
       <c r="R5" t="n">
-        <v>6371267</v>
+        <v>6371302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122605578</v>
+        <v>122605621</v>
       </c>
       <c r="B6" t="n">
-        <v>94844</v>
+        <v>94846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599123</v>
+        <v>599116</v>
       </c>
       <c r="R6" t="n">
-        <v>6371303</v>
+        <v>6371319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122783407</v>
+        <v>122785481</v>
       </c>
       <c r="B8" t="n">
-        <v>90964</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,37 +1321,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598958</v>
+        <v>598943</v>
       </c>
       <c r="R8" t="n">
-        <v>6371064</v>
+        <v>6371087</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122782695</v>
+        <v>122782823</v>
       </c>
       <c r="B9" t="n">
-        <v>90904</v>
+        <v>94846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599109</v>
+        <v>599138</v>
       </c>
       <c r="R9" t="n">
-        <v>6371243</v>
+        <v>6371196</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1512,7 +1517,7 @@
         <v>122785740</v>
       </c>
       <c r="B10" t="n">
-        <v>94844</v>
+        <v>94846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122782823</v>
+        <v>122783407</v>
       </c>
       <c r="B11" t="n">
-        <v>94844</v>
+        <v>90964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1628,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,13 +1656,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599138</v>
+        <v>598958</v>
       </c>
       <c r="R11" t="n">
-        <v>6371196</v>
+        <v>6371064</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122784093</v>
+        <v>122782695</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>90904</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,41 +1734,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598954</v>
+        <v>599109</v>
       </c>
       <c r="R12" t="n">
-        <v>6371068</v>
+        <v>6371243</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1819,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122785481</v>
+        <v>122784093</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,27 +1836,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598943</v>
+        <v>598954</v>
       </c>
       <c r="R13" t="n">
-        <v>6371087</v>
+        <v>6371068</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122605578</v>
+        <v>122607678</v>
       </c>
       <c r="B3" t="n">
         <v>94846</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599123</v>
+        <v>599125</v>
       </c>
       <c r="R3" t="n">
-        <v>6371303</v>
+        <v>6371302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607634</v>
+        <v>122605578</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>94846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599119</v>
+        <v>599123</v>
       </c>
       <c r="R4" t="n">
-        <v>6371267</v>
+        <v>6371303</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607678</v>
+        <v>122611560</v>
       </c>
       <c r="B5" t="n">
-        <v>94846</v>
+        <v>90964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599125</v>
+        <v>599157</v>
       </c>
       <c r="R5" t="n">
-        <v>6371302</v>
+        <v>6371219</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,17 +1061,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122605621</v>
+        <v>122607634</v>
       </c>
       <c r="B6" t="n">
-        <v>94846</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599116</v>
+        <v>599119</v>
       </c>
       <c r="R6" t="n">
-        <v>6371319</v>
+        <v>6371267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122611560</v>
+        <v>122605621</v>
       </c>
       <c r="B7" t="n">
-        <v>90964</v>
+        <v>94846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,48 +1215,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599157</v>
+        <v>599116</v>
       </c>
       <c r="R7" t="n">
-        <v>6371219</v>
+        <v>6371319</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1265,28 +1276,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607745</v>
+        <v>122605621</v>
       </c>
       <c r="B2" t="n">
-        <v>94846</v>
+        <v>94854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599042</v>
+        <v>599116</v>
       </c>
       <c r="R2" t="n">
-        <v>6371309</v>
+        <v>6371319</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607678</v>
+        <v>122611560</v>
       </c>
       <c r="B3" t="n">
-        <v>94846</v>
+        <v>90972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599125</v>
+        <v>599157</v>
       </c>
       <c r="R3" t="n">
-        <v>6371302</v>
+        <v>6371219</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,17 +857,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122605578</v>
+        <v>122607678</v>
       </c>
       <c r="B4" t="n">
-        <v>94846</v>
+        <v>94854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599123</v>
+        <v>599125</v>
       </c>
       <c r="R4" t="n">
-        <v>6371303</v>
+        <v>6371302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611560</v>
+        <v>122607634</v>
       </c>
       <c r="B5" t="n">
-        <v>90964</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,48 +1011,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599157</v>
+        <v>599119</v>
       </c>
       <c r="R5" t="n">
-        <v>6371219</v>
+        <v>6371267</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,28 +1072,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607634</v>
+        <v>122607745</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>94854</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599119</v>
+        <v>599042</v>
       </c>
       <c r="R6" t="n">
-        <v>6371267</v>
+        <v>6371309</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122605621</v>
+        <v>122605578</v>
       </c>
       <c r="B7" t="n">
-        <v>94846</v>
+        <v>94854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599116</v>
+        <v>599123</v>
       </c>
       <c r="R7" t="n">
-        <v>6371319</v>
+        <v>6371303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122785481</v>
+        <v>122785740</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>94854</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,46 +1317,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598943</v>
+        <v>599069</v>
       </c>
       <c r="R8" t="n">
-        <v>6371087</v>
+        <v>6371302</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,7 +1410,7 @@
         <v>122782823</v>
       </c>
       <c r="B9" t="n">
-        <v>94846</v>
+        <v>94854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122785740</v>
+        <v>122783407</v>
       </c>
       <c r="B10" t="n">
-        <v>94846</v>
+        <v>90972</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,25 +1521,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,13 +1549,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599069</v>
+        <v>598958</v>
       </c>
       <c r="R10" t="n">
-        <v>6371302</v>
+        <v>6371064</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122783407</v>
+        <v>122782695</v>
       </c>
       <c r="B11" t="n">
-        <v>90964</v>
+        <v>90912</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,21 +1627,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,13 +1651,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598958</v>
+        <v>599109</v>
       </c>
       <c r="R11" t="n">
-        <v>6371064</v>
+        <v>6371243</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122782695</v>
+        <v>122784093</v>
       </c>
       <c r="B12" t="n">
-        <v>90904</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,37 +1729,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5445</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599109</v>
+        <v>598954</v>
       </c>
       <c r="R12" t="n">
-        <v>6371243</v>
+        <v>6371068</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122784093</v>
+        <v>122785481</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,26 +1835,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598954</v>
+        <v>598943</v>
       </c>
       <c r="R13" t="n">
-        <v>6371068</v>
+        <v>6371087</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122605621</v>
+        <v>122607745</v>
       </c>
       <c r="B2" t="n">
         <v>94854</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599116</v>
+        <v>599042</v>
       </c>
       <c r="R2" t="n">
-        <v>6371319</v>
+        <v>6371309</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611560</v>
+        <v>122605621</v>
       </c>
       <c r="B3" t="n">
-        <v>90972</v>
+        <v>94854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,48 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599157</v>
+        <v>599116</v>
       </c>
       <c r="R3" t="n">
-        <v>6371219</v>
+        <v>6371319</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,28 +850,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -999,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607634</v>
+        <v>122611560</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>90972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,41 +993,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599119</v>
+        <v>599157</v>
       </c>
       <c r="R5" t="n">
-        <v>6371267</v>
+        <v>6371219</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,17 +1061,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607745</v>
+        <v>122605578</v>
       </c>
       <c r="B6" t="n">
         <v>94854</v>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599042</v>
+        <v>599123</v>
       </c>
       <c r="R6" t="n">
-        <v>6371309</v>
+        <v>6371303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122605578</v>
+        <v>122607634</v>
       </c>
       <c r="B7" t="n">
-        <v>94854</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599123</v>
+        <v>599119</v>
       </c>
       <c r="R7" t="n">
-        <v>6371303</v>
+        <v>6371267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122785740</v>
+        <v>122784093</v>
       </c>
       <c r="B8" t="n">
-        <v>94854</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,41 +1317,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599069</v>
+        <v>598954</v>
       </c>
       <c r="R8" t="n">
-        <v>6371302</v>
+        <v>6371068</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122782823</v>
+        <v>122782695</v>
       </c>
       <c r="B9" t="n">
-        <v>94854</v>
+        <v>90912</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1423,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599138</v>
+        <v>599109</v>
       </c>
       <c r="R9" t="n">
-        <v>6371196</v>
+        <v>6371243</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1611,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122782695</v>
+        <v>122785481</v>
       </c>
       <c r="B11" t="n">
-        <v>90912</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,37 +1631,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5445</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599109</v>
+        <v>598943</v>
       </c>
       <c r="R11" t="n">
-        <v>6371243</v>
+        <v>6371087</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122784093</v>
+        <v>122782823</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>94854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,45 +1734,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598954</v>
+        <v>599138</v>
       </c>
       <c r="R12" t="n">
-        <v>6371068</v>
+        <v>6371196</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1819,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122785481</v>
+        <v>122785740</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>94854</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,46 +1836,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598943</v>
+        <v>599069</v>
       </c>
       <c r="R13" t="n">
-        <v>6371087</v>
+        <v>6371302</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122784093</v>
+        <v>122783407</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>90972</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,41 +1321,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598954</v>
+        <v>598958</v>
       </c>
       <c r="R8" t="n">
-        <v>6371068</v>
+        <v>6371064</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122782695</v>
+        <v>122782823</v>
       </c>
       <c r="B9" t="n">
-        <v>90912</v>
+        <v>94854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599109</v>
+        <v>599138</v>
       </c>
       <c r="R9" t="n">
-        <v>6371243</v>
+        <v>6371196</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1513,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122783407</v>
+        <v>122785481</v>
       </c>
       <c r="B10" t="n">
-        <v>90972</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,37 +1525,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598958</v>
+        <v>598943</v>
       </c>
       <c r="R10" t="n">
-        <v>6371064</v>
+        <v>6371087</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1615,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122785481</v>
+        <v>122782695</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>90912</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,42 +1632,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598943</v>
+        <v>599109</v>
       </c>
       <c r="R11" t="n">
-        <v>6371087</v>
+        <v>6371243</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1722,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122782823</v>
+        <v>122784093</v>
       </c>
       <c r="B12" t="n">
-        <v>94854</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,41 +1730,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599138</v>
+        <v>598954</v>
       </c>
       <c r="R12" t="n">
-        <v>6371196</v>
+        <v>6371068</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122782823</v>
+        <v>122785740</v>
       </c>
       <c r="B9" t="n">
         <v>94854</v>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599138</v>
+        <v>599069</v>
       </c>
       <c r="R9" t="n">
-        <v>6371196</v>
+        <v>6371302</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122784093</v>
+        <v>122782823</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>94854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,45 +1730,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598954</v>
+        <v>599138</v>
       </c>
       <c r="R12" t="n">
-        <v>6371068</v>
+        <v>6371196</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122785740</v>
+        <v>122784093</v>
       </c>
       <c r="B13" t="n">
-        <v>94854</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,41 +1832,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599069</v>
+        <v>598954</v>
       </c>
       <c r="R13" t="n">
-        <v>6371302</v>
+        <v>6371068</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -1718,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122782823</v>
+        <v>122784093</v>
       </c>
       <c r="B12" t="n">
-        <v>94854</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,41 +1730,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599138</v>
+        <v>598954</v>
       </c>
       <c r="R12" t="n">
-        <v>6371196</v>
+        <v>6371068</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122784093</v>
+        <v>122782823</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>94854</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,45 +1836,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598954</v>
+        <v>599138</v>
       </c>
       <c r="R13" t="n">
-        <v>6371068</v>
+        <v>6371196</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122783407</v>
+        <v>122784093</v>
       </c>
       <c r="B8" t="n">
-        <v>90972</v>
+        <v>57497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,37 +1321,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598958</v>
+        <v>598954</v>
       </c>
       <c r="R8" t="n">
-        <v>6371064</v>
+        <v>6371068</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122785740</v>
+        <v>122783407</v>
       </c>
       <c r="B9" t="n">
-        <v>94854</v>
+        <v>90975</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1423,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,13 +1451,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599069</v>
+        <v>598958</v>
       </c>
       <c r="R9" t="n">
-        <v>6371302</v>
+        <v>6371064</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122785481</v>
+        <v>122782695</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>90915</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,42 +1529,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598943</v>
+        <v>599109</v>
       </c>
       <c r="R10" t="n">
-        <v>6371087</v>
+        <v>6371243</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122782695</v>
+        <v>122782823</v>
       </c>
       <c r="B11" t="n">
-        <v>90912</v>
+        <v>94857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,25 +1627,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599109</v>
+        <v>599138</v>
       </c>
       <c r="R11" t="n">
-        <v>6371243</v>
+        <v>6371196</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1718,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122784093</v>
+        <v>122785481</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>57634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,26 +1733,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598954</v>
+        <v>598943</v>
       </c>
       <c r="R12" t="n">
-        <v>6371068</v>
+        <v>6371087</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1824,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122782823</v>
+        <v>122785740</v>
       </c>
       <c r="B13" t="n">
-        <v>94854</v>
+        <v>94857</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599138</v>
+        <v>599069</v>
       </c>
       <c r="R13" t="n">
-        <v>6371196</v>
+        <v>6371302</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122784093</v>
+        <v>122782695</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>90917</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,41 +1321,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598954</v>
+        <v>599109</v>
       </c>
       <c r="R8" t="n">
-        <v>6371068</v>
+        <v>6371243</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,7 +1410,7 @@
         <v>122783407</v>
       </c>
       <c r="B9" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122782695</v>
+        <v>122785740</v>
       </c>
       <c r="B10" t="n">
-        <v>90915</v>
+        <v>94859</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,25 +1521,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599109</v>
+        <v>599069</v>
       </c>
       <c r="R10" t="n">
-        <v>6371243</v>
+        <v>6371302</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1615,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122782823</v>
+        <v>122785481</v>
       </c>
       <c r="B11" t="n">
-        <v>94857</v>
+        <v>57634</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,41 +1623,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2671</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599138</v>
+        <v>598943</v>
       </c>
       <c r="R11" t="n">
-        <v>6371196</v>
+        <v>6371087</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1717,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122785481</v>
+        <v>122784093</v>
       </c>
       <c r="B12" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1733,27 +1734,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598943</v>
+        <v>598954</v>
       </c>
       <c r="R12" t="n">
-        <v>6371087</v>
+        <v>6371068</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1824,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122785740</v>
+        <v>122782823</v>
       </c>
       <c r="B13" t="n">
-        <v>94857</v>
+        <v>94859</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599069</v>
+        <v>599138</v>
       </c>
       <c r="R13" t="n">
-        <v>6371302</v>
+        <v>6371196</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>122782695</v>
       </c>
       <c r="B8" t="n">
-        <v>90917</v>
+        <v>90923</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122783407</v>
+        <v>122785740</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>94865</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598958</v>
+        <v>599069</v>
       </c>
       <c r="R9" t="n">
-        <v>6371064</v>
+        <v>6371302</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122785740</v>
+        <v>122785481</v>
       </c>
       <c r="B10" t="n">
-        <v>94859</v>
+        <v>57634</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,41 +1521,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599069</v>
+        <v>598943</v>
       </c>
       <c r="R10" t="n">
-        <v>6371302</v>
+        <v>6371087</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122785481</v>
+        <v>122783407</v>
       </c>
       <c r="B11" t="n">
-        <v>57634</v>
+        <v>90983</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,42 +1632,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598943</v>
+        <v>598958</v>
       </c>
       <c r="R11" t="n">
-        <v>6371087</v>
+        <v>6371064</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>122782823</v>
       </c>
       <c r="B13" t="n">
-        <v>94859</v>
+        <v>94865</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607745</v>
+        <v>122605578</v>
       </c>
       <c r="B2" t="n">
-        <v>94854</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599042</v>
+        <v>599123</v>
       </c>
       <c r="R2" t="n">
-        <v>6371309</v>
+        <v>6371303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,12 +775,7 @@
         <v>122605621</v>
       </c>
       <c r="B3" t="n">
-        <v>94854</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,12 +872,7 @@
         <v>122607678</v>
       </c>
       <c r="B4" t="n">
-        <v>94854</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,60 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611560</v>
+        <v>122607745</v>
       </c>
       <c r="B5" t="n">
-        <v>90972</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599157</v>
+        <v>599042</v>
       </c>
       <c r="R5" t="n">
-        <v>6371219</v>
+        <v>6371309</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,28 +1034,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1101,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122605578</v>
+        <v>122782823</v>
       </c>
       <c r="B6" t="n">
-        <v>94854</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599123</v>
+        <v>599138</v>
       </c>
       <c r="R6" t="n">
-        <v>6371303</v>
+        <v>6371196</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607634</v>
+        <v>122785378</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599119</v>
+        <v>598983</v>
       </c>
       <c r="R7" t="n">
-        <v>6371267</v>
+        <v>6370961</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1273,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,49 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122783407</v>
+        <v>122785740</v>
       </c>
       <c r="B8" t="n">
-        <v>90986</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598958</v>
+        <v>599069</v>
       </c>
       <c r="R8" t="n">
-        <v>6371064</v>
+        <v>6371302</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122782695</v>
+        <v>122611560</v>
       </c>
       <c r="B9" t="n">
-        <v>90926</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,37 +1365,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599109</v>
+        <v>599157</v>
       </c>
       <c r="R9" t="n">
-        <v>6371243</v>
+        <v>6371219</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1477,12 +1426,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,55 +1450,51 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122785740</v>
+        <v>122783407</v>
       </c>
       <c r="B10" t="n">
-        <v>94868</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599069</v>
+        <v>598958</v>
       </c>
       <c r="R10" t="n">
-        <v>6371302</v>
+        <v>6371064</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,15 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122784093</v>
+        <v>122782695</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1627,41 +1577,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598954</v>
+        <v>599109</v>
       </c>
       <c r="R11" t="n">
-        <v>6371068</v>
+        <v>6371243</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1717,15 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122782823</v>
+        <v>122784093</v>
       </c>
       <c r="B12" t="n">
-        <v>94868</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,37 +1674,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599138</v>
+        <v>598954</v>
       </c>
       <c r="R12" t="n">
-        <v>6371196</v>
+        <v>6371068</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1819,58 +1764,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122785481</v>
+        <v>122607634</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598943</v>
+        <v>599119</v>
       </c>
       <c r="R13" t="n">
-        <v>6371087</v>
+        <v>6371267</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1894,12 +1829,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,15 +1849,219 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122785481</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hemängen, Hemängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>598943</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6371087</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122785603</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hemängen, Hemängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>598980</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6371184</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5153-2025 artfynd.xlsx
+++ b/artfynd/A 5153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122605578</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122605621</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122607678</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122607745</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122782823</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122785378</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122785740</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122611560</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122783407</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122782695</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1761,6 +1816,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122784093</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1858,6 +1918,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122607634</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,6 +2025,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122785481</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2062,8 +2132,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122785603</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>